--- a/Configs/GameConfig/Datas/roguelike_relic.xlsx
+++ b/Configs/GameConfig/Datas/roguelike_relic.xlsx
@@ -288,7 +288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,28 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>coin_badge</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>?????? +25%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AddGoldMultiplier,0.25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
